--- a/SGC-CKN/Excel/9b45a05f-1828-4571-a5a9-9f72b3b9d3c9_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-100_D800_14-03-2026.xlsx
+++ b/SGC-CKN/Excel/9b45a05f-1828-4571-a5a9-9f72b3b9d3c9_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-100_D800_14-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="74">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P7-100</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>M3-3.1.1.2.6</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -106,13 +106,10 @@
 14/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">04:00
@@ -178,7 +175,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:00
@@ -192,7 +189,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1. Cát sạn, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát lẫn sạn màu xám ghi, xám vàng, xám xanh, TT chặt vừa đến rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">12:00
@@ -205,9 +202,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">13:30
 14/03/2026</t>
   </si>
@@ -219,7 +213,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội, sỏi, sạn cát, đá khoảng, đa sắc, TT chặt đến rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:48
@@ -1249,24 +1243,24 @@
         <v>81.6</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-8.9</v>
@@ -1284,24 +1278,24 @@
         <v>2</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>36</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>37</v>
       </c>
       <c r="F13" s="13">
         <v>-10.9</v>
@@ -1319,24 +1313,24 @@
         <v>5.73</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="E14" s="18" t="s">
         <v>40</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>41</v>
       </c>
       <c r="F14" s="16">
         <v>-19.5</v>
@@ -1354,24 +1348,24 @@
         <v>4.69</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="E15" s="21" t="s">
         <v>44</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>45</v>
       </c>
       <c r="F15" s="19">
         <v>-23.8</v>
@@ -1389,24 +1383,24 @@
         <v>2.86</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="E16" s="24" t="s">
         <v>48</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>49</v>
       </c>
       <c r="F16" s="22">
         <v>-27.800000000000004</v>
@@ -1424,24 +1418,24 @@
         <v>10.42</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="E17" s="27" t="s">
         <v>52</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>53</v>
       </c>
       <c r="F17" s="25">
         <v>-37.00000000000001</v>
@@ -1459,24 +1453,24 @@
         <v>2.54</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>55</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>56</v>
       </c>
       <c r="F18" s="28">
         <v>-39.20000000000001</v>
@@ -1494,24 +1488,24 @@
         <v>11.25</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>59</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>61</v>
       </c>
       <c r="F19" s="31">
         <v>-40.70000000000001</v>
@@ -1529,24 +1523,24 @@
         <v>3.43</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>63</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>65</v>
       </c>
       <c r="F20" s="34">
         <v>-44.70000000000001</v>
@@ -1564,12 +1558,12 @@
         <v>8.4</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1675,31 +1669,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1739,7 +1733,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1768,7 +1762,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1797,7 +1791,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1826,7 +1820,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1855,7 +1849,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1884,7 +1878,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1913,7 +1907,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1942,7 +1936,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1971,7 +1965,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1994,13 +1988,13 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D12" s="39">
         <v>10</v>

--- a/SGC-CKN/Excel/9b45a05f-1828-4571-a5a9-9f72b3b9d3c9_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-100_D800_14-03-2026.xlsx
+++ b/SGC-CKN/Excel/9b45a05f-1828-4571-a5a9-9f72b3b9d3c9_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-100_D800_14-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="73">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGC-KCN0001</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">03:30
@@ -106,6 +106,9 @@
 14/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
@@ -123,9 +126,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">06:30
 14/03/2026</t>
   </si>
@@ -147,7 +147,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">08:26
@@ -159,9 +159,6 @@
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:00
@@ -258,7 +255,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -334,11 +331,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF134E4A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -351,7 +343,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -426,11 +418,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99F6E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -526,7 +513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -627,22 +614,13 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1243,24 +1221,24 @@
         <v>81.6</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-8.9</v>
@@ -1278,21 +1256,21 @@
         <v>2</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>36</v>
@@ -1313,7 +1291,7 @@
         <v>5.73</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1348,7 +1326,7 @@
         <v>4.69</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1383,198 +1361,198 @@
         <v>2.86</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="E16" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="22">
+      <c r="F16" s="19">
         <v>-27.800000000000004</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="19">
         <v>-37.00000000000001</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="19">
         <v>0.88</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="19">
         <v>9.2</v>
       </c>
       <c r="J16" s="8">
         <v>10.42</v>
       </c>
-      <c r="K16" s="23" t="s">
-        <v>9</v>
+      <c r="K16" s="20" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="D17" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="E17" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="F17" s="22">
         <v>-37.00000000000001</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="22">
         <v>-39.20000000000001</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="22">
         <v>0.87</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="22">
         <v>2.2</v>
       </c>
       <c r="J17" s="12">
         <v>2.54</v>
       </c>
-      <c r="K17" s="26" t="s">
-        <v>9</v>
+      <c r="K17" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="28">
+      <c r="F18" s="25">
         <v>-39.20000000000001</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="25">
         <v>-40.70000000000001</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="25">
         <v>0.13</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="25">
         <v>1.5</v>
       </c>
       <c r="J18" s="8">
         <v>11.25</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K18" s="26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="B19" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="33" t="s">
+      <c r="E19" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="31">
+      <c r="F19" s="28">
         <v>-40.70000000000001</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="28">
         <v>-44.70000000000001</v>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="28">
         <v>1.17</v>
       </c>
-      <c r="I19" s="31">
+      <c r="I19" s="28">
         <v>4</v>
       </c>
       <c r="J19" s="12">
         <v>3.43</v>
       </c>
-      <c r="K19" s="32" t="s">
-        <v>9</v>
+      <c r="K19" s="29" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
+      <c r="D20" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="E20" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="F20" s="34">
+      <c r="F20" s="31">
         <v>-44.70000000000001</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="31">
         <v>-45.400000000000006</v>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="31">
         <v>0.08</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="31">
         <v>0.7</v>
       </c>
       <c r="J20" s="8">
         <v>8.4</v>
       </c>
-      <c r="K20" s="35" t="s">
-        <v>9</v>
+      <c r="K20" s="32" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
+      <c r="A23" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1656,7 +1634,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1669,31 +1647,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1733,7 +1711,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1762,7 +1740,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1823,22 +1801,22 @@
         <v>42</v>
       </c>
       <c r="D6" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="19">
         <v>-23.8</v>
       </c>
       <c r="F6" s="19">
-        <v>-27.8</v>
+        <v>-37</v>
       </c>
       <c r="G6" s="19">
-        <v>1.4</v>
+        <v>2.28</v>
       </c>
       <c r="H6" s="19">
-        <v>4</v>
-      </c>
-      <c r="I6" s="12">
-        <v>2.86</v>
+        <v>13.2</v>
+      </c>
+      <c r="I6" s="8">
+        <v>5.78</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1849,25 +1827,25 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-27.8</v>
+        <v>-37</v>
       </c>
       <c r="F7" s="22">
-        <v>-37</v>
+        <v>-39.2</v>
       </c>
       <c r="G7" s="22">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="H7" s="22">
-        <v>9.2</v>
-      </c>
-      <c r="I7" s="8">
-        <v>10.42</v>
+        <v>2.2</v>
+      </c>
+      <c r="I7" s="12">
+        <v>2.54</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1878,25 +1856,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-37</v>
+        <v>-39.2</v>
       </c>
       <c r="F8" s="25">
-        <v>-39.2</v>
+        <v>-40.7</v>
       </c>
       <c r="G8" s="25">
-        <v>0.87</v>
+        <v>0.13</v>
       </c>
       <c r="H8" s="25">
-        <v>2.2</v>
-      </c>
-      <c r="I8" s="12">
-        <v>2.54</v>
+        <v>1.5</v>
+      </c>
+      <c r="I8" s="8">
+        <v>11.25</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1907,25 +1885,25 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-39.2</v>
+        <v>-40.7</v>
       </c>
       <c r="F9" s="28">
-        <v>-40.7</v>
+        <v>-44.7</v>
       </c>
       <c r="G9" s="28">
-        <v>0.13</v>
+        <v>1.17</v>
       </c>
       <c r="H9" s="28">
-        <v>1.5</v>
-      </c>
-      <c r="I9" s="8">
-        <v>11.25</v>
+        <v>4</v>
+      </c>
+      <c r="I9" s="12">
+        <v>3.43</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1936,82 +1914,53 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>-40.7</v>
+        <v>-44.7</v>
       </c>
       <c r="F10" s="31">
-        <v>-44.7</v>
+        <v>-45.4</v>
       </c>
       <c r="G10" s="31">
-        <v>1.17</v>
+        <v>0.08</v>
       </c>
       <c r="H10" s="31">
-        <v>4</v>
-      </c>
-      <c r="I10" s="12">
-        <v>3.43</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
+        <v>0.7</v>
+      </c>
+      <c r="I10" s="8">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="36">
         <v>10</v>
       </c>
-      <c r="B11" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="34">
-        <v>1</v>
-      </c>
-      <c r="E11" s="34">
-        <v>-44.7</v>
-      </c>
-      <c r="F11" s="34">
+      <c r="E11" s="36">
+        <v>-2.1</v>
+      </c>
+      <c r="F11" s="36">
         <v>-45.4</v>
       </c>
-      <c r="G11" s="34">
-        <v>0.08</v>
-      </c>
-      <c r="H11" s="34">
-        <v>0.7</v>
-      </c>
-      <c r="I11" s="8">
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="39">
-        <v>10</v>
-      </c>
-      <c r="E12" s="39">
-        <v>-2.1</v>
-      </c>
-      <c r="F12" s="39">
-        <v>-45.4</v>
-      </c>
-      <c r="G12" s="39">
+      <c r="G11" s="36">
         <v>8.03</v>
       </c>
-      <c r="H12" s="39">
+      <c r="H11" s="36">
         <v>43.3</v>
       </c>
-      <c r="I12" s="39">
+      <c r="I11" s="36">
         <v>5.39</v>
       </c>
     </row>
